--- a/release-branch/StructureDefinition-bc-merge-patient.xlsx
+++ b/release-branch/StructureDefinition-bc-merge-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-27T22:30:17+00:00</t>
+    <t>2025-10-07T21:05:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4115,7 +4115,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>169</v>
       </c>
@@ -5765,7 +5765,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>281</v>
       </c>
@@ -6939,7 +6939,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>346</v>
       </c>
@@ -7875,7 +7875,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>392</v>
       </c>
@@ -8222,7 +8222,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>407</v>
       </c>
@@ -8454,7 +8454,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>412</v>
       </c>
@@ -9033,7 +9033,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>430</v>
       </c>
@@ -9380,7 +9380,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
         <v>440</v>
       </c>
@@ -9497,7 +9497,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>442</v>
       </c>
@@ -9729,7 +9729,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>450</v>
       </c>
@@ -10318,7 +10318,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>471</v>
       </c>
@@ -12081,7 +12081,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
         <v>575</v>
       </c>
@@ -14562,7 +14562,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
         <v>683</v>
       </c>
@@ -14913,7 +14913,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="106" hidden="true">
+    <row r="106">
       <c r="A106" t="s" s="2">
         <v>691</v>
       </c>
@@ -15385,12 +15385,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO109">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/release-branch/StructureDefinition-bc-merge-patient.xlsx
+++ b/release-branch/StructureDefinition-bc-merge-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-07T21:05:34+00:00</t>
+    <t>2025-11-21T23:55:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-merge-patient.xlsx
+++ b/release-branch/StructureDefinition-bc-merge-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-21T23:55:27+00:00</t>
+    <t>2026-01-12T21:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-merge-patient.xlsx
+++ b/release-branch/StructureDefinition-bc-merge-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T21:43:07+00:00</t>
+    <t>2026-01-22T19:20:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-merge-patient.xlsx
+++ b/release-branch/StructureDefinition-bc-merge-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T19:20:19+00:00</t>
+    <t>2026-02-17T21:23:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-merge-patient.xlsx
+++ b/release-branch/StructureDefinition-bc-merge-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T21:23:45+00:00</t>
+    <t>2026-03-17T18:19:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-merge-patient.xlsx
+++ b/release-branch/StructureDefinition-bc-merge-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T18:19:20+00:00</t>
+    <t>2026-03-25T21:29:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
